--- a/data/trans_orig/IP31KM01_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM01_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34698</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31929</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>36509</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>92,69%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>85,29%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>97,53%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>79</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>44595</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>41767</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>46070</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>95,91%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>89,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>99,09%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41872</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38391</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44060</t>
+          <t>42237</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>86466</t>
+          <t>75700</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>81894</t>
+          <t>72371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89126</t>
+          <t>77954</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>90,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>5506</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,31%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,47%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,71%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>1900</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>425</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>4728</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>10,17%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>1679</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1225</t>
+          <t>444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>5313</t>
+          <t>4416</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2653</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>7745</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>9,67%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37435</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>46495</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45285</t>
+          <t>42681</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>91779</t>
+          <t>80116</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>144536</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>137641</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>149435</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>87,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>95,16%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>145408</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>137601</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>150221</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>91,28%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>86,38%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>94,3%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>167936</t>
+          <t>133057</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160364</t>
+          <t>126864</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>173042</t>
+          <t>137484</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>313345</t>
+          <t>277592</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>303900</t>
+          <t>269705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>321217</t>
+          <t>284207</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>13891</t>
+          <t>12506</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>7607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21698</t>
+          <t>19401</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>12461</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>18654</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>27914</t>
+          <t>24968</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20042</t>
+          <t>18353</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>37359</t>
+          <t>32855</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,86%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157042</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181959</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341259</t>
+          <t>302560</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>181390</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>171050</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>188063</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>90,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>85,47%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>93,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>213</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>157901</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>150186</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>163584</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>86,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>94,52%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>192894</t>
+          <t>158893</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>182313</t>
+          <t>151081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>200072</t>
+          <t>164492</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,97%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>350796</t>
+          <t>340283</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>338856</t>
+          <t>328225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>360033</t>
+          <t>349347</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>90,79%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15171</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>12063</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22886</t>
+          <t>29076</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19596</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12418</t>
+          <t>10180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>23591</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>34767</t>
+          <t>34515</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25530</t>
+          <t>25451</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>46707</t>
+          <t>46573</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385563</t>
+          <t>374798</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>256941</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>244604</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>266712</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>87,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>83,7%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>91,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>247944</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>237940</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>256736</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>90,4%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>86,75%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>264623</t>
+          <t>227821</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>243632</t>
+          <t>217641</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>276334</t>
+          <t>235199</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>512567</t>
+          <t>484763</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>490295</t>
+          <t>468105</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>528570</t>
+          <t>496863</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>35280</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>25509</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>47617</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>26323</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17531</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>36327</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>9,6%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>13,25%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40376</t>
+          <t>27516</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>20138</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>61367</t>
+          <t>37696</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>66699</t>
+          <t>62795</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50696</t>
+          <t>50695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>88971</t>
+          <t>79453</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>274267</t>
+          <t>292221</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>304999</t>
+          <t>255337</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>579266</t>
+          <t>547558</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>617565</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>601064</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>631556</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>89,92%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>87,51%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>91,95%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>831</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>595849</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>580984</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>606819</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>91,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>88,95%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>853</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>667324</t>
+          <t>560772</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>646433</t>
+          <t>547624</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>682126</t>
+          <t>572223</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1263174</t>
+          <t>1178336</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1238024</t>
+          <t>1159390</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1281985</t>
+          <t>1197619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,77%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>69259</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>55268</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>85760</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>8,05%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>12,49%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>57285</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>46315</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>72150</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>8,77%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7,09%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>11,05%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>57436</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62607</t>
+          <t>45985</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>98300</t>
+          <t>70584</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>134693</t>
+          <t>126695</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>115882</t>
+          <t>107412</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159843</t>
+          <t>145641</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,16%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
